--- a/slides/01-IntroR/data/df_age.xlsx
+++ b/slides/01-IntroR/data/df_age.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
